--- a/data/seed/portfolio/L-2025-1541/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2025-1541/vypiska_2026-07_09.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I154"/>
+  <dimension ref="A1:I179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -560,31 +560,31 @@
       </c>
       <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="n">
-        <v>2795000</v>
+        <v>8125000</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Xiva Metall MChJ</t>
+          <t>Ziyo Avto Savdo AJ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>297071667</t>
+          <t>213072228</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000210264664001</t>
+          <t>20208000697884713001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Shartnoma №262/26 bo'yicha oldindan to'lov</t>
+          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №9051</t>
         </is>
       </c>
     </row>
@@ -600,32 +600,32 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>22799000</v>
+        <v>20683000</v>
       </c>
       <c r="D11" s="2" t="n"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mehnat Polimer XK</t>
+          <t>Nukus Logistik MChJ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>203106510</t>
+          <t>210651038</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000866576450001</t>
+          <t>20208000657645067001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>TRANSPORT XIZMATLARI UCHUN TO'LOV, SHARTNOMA №217/26</t>
+          <t>ОПЛАТА ЗА СЫРЬЕ ПО ДОГОВОРУ №186/26 ОТ 01.07.2026, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -642,38 +642,38 @@
       </c>
       <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="n">
-        <v>37554000</v>
+        <v>35332000</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Xiva Metall MChJ</t>
+          <t>Denov Moy MChJ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>297071667</t>
+          <t>335454567</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000210264664001</t>
+          <t>20208000523414352001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №7352 02.07.2026, QQS bilan</t>
+          <t>Оплата за продукцию по договору №19/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>03.07.2026</t>
+          <t>02.07.2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -683,31 +683,31 @@
       </c>
       <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="n">
-        <v>6140000</v>
+        <v>3289000</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gulshan Meva-Sabzavot AJ</t>
+          <t>Shodlik Poligraf AJ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>368012667</t>
+          <t>307166732</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20208000578660997001</t>
+          <t>20208000026466438001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №6634 от 03.07.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за товар по договору №48/26 от 02.07.2026</t>
         </is>
       </c>
     </row>
@@ -722,40 +722,40 @@
           <t>104</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n">
-        <v>15931000</v>
-      </c>
-      <c r="D14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n">
+        <v>11645000</v>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Urganch Meva-Sabzavot MChJ</t>
+          <t>Shodlik Poligraf AJ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>341863247</t>
+          <t>307166732</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000901102914001</t>
+          <t>20208000026466438001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №81/26</t>
+          <t>Оплата по с/ф №8829 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>03.07.2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -765,31 +765,31 @@
       </c>
       <c r="C15" s="2" t="n"/>
       <c r="D15" s="2" t="n">
-        <v>4602000</v>
+        <v>5406000</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Xiva Metall MChJ</t>
+          <t>Denov Moy MChJ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>297071667</t>
+          <t>335454567</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20208000210264664001</t>
+          <t>20208000523414352001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Shartnoma №286/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата по с/ф №6175 за поставленный товар</t>
         </is>
       </c>
     </row>
@@ -806,31 +806,31 @@
       </c>
       <c r="C16" s="2" t="n"/>
       <c r="D16" s="2" t="n">
-        <v>2539000</v>
+        <v>42825000</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Marg'ilon Trans Servis MChJ</t>
+          <t>Denov Moy MChJ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>384130722</t>
+          <t>335454567</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000896978847001</t>
+          <t>20208000523414352001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Shartnoma №189/26 bo'yicha oldindan to'lov</t>
+          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №149 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
     </row>
@@ -845,33 +845,33 @@
           <t>107</t>
         </is>
       </c>
-      <c r="C17" s="2" t="n">
-        <v>13007000</v>
-      </c>
-      <c r="D17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n">
+        <v>12139000</v>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ishonch Trans Servis XK</t>
+          <t>Shodlik Poligraf AJ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>352219763</t>
+          <t>307166732</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20208000492874273001</t>
+          <t>20208000026466438001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №4981</t>
+          <t>Предоплата за товар по договору №49/26 от 06.07.2026</t>
         </is>
       </c>
     </row>
@@ -887,34 +887,39 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>33429000</v>
+        <v>17195000</v>
       </c>
       <c r="D18" s="2" t="n"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Namangan Non XK</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>203301054</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000769946250001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Ish haqi to'lovi iyun 2026 (plastik kartalarga)</t>
+          <t>Оплата за упаковочные материалы, с/ф №711</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07.07.2026</t>
+          <t>06.07.2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -922,33 +927,28 @@
           <t>109</t>
         </is>
       </c>
-      <c r="C19" s="2" t="n"/>
-      <c r="D19" s="2" t="n">
-        <v>5636000</v>
-      </c>
+      <c r="C19" s="2" t="n">
+        <v>33429000</v>
+      </c>
+      <c r="D19" s="2" t="n"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Xiva Metall MChJ</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>297071667</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20208000210264664001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma 21/26, QQS 12%</t>
+          <t>Заработная плата за июнь 2026 г. (перечисление на пластиковые карты)</t>
         </is>
       </c>
     </row>
@@ -963,23 +963,23 @@
           <t>110</t>
         </is>
       </c>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="n">
-        <v>5156000</v>
-      </c>
+      <c r="C20" s="2" t="n">
+        <v>26802000</v>
+      </c>
+      <c r="D20" s="2" t="n"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Shahrisabz Polimer AJ</t>
+          <t>Nukus Logistik MChJ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>307354545</t>
+          <t>210651038</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20208000745234143001</t>
+          <t>20208000657645067001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №223/26, QQS 12%</t>
+          <t>Tovarlar uchun to'lov h/f №3740</t>
         </is>
       </c>
     </row>
@@ -1004,40 +1004,40 @@
           <t>111</t>
         </is>
       </c>
-      <c r="C21" s="2" t="n">
-        <v>16013000</v>
-      </c>
-      <c r="D21" s="2" t="n"/>
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n">
+        <v>16793000</v>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Mehnat Polimer XK</t>
+          <t>Shodlik Poligraf AJ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>203106510</t>
+          <t>307166732</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000866576450001</t>
+          <t>20208000026466438001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №2834</t>
+          <t>Tovar uchun to'lov, h/f №6693 08.07.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09.07.2026</t>
+          <t>08.07.2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1047,21 +1047,21 @@
       </c>
       <c r="C22" s="2" t="n"/>
       <c r="D22" s="2" t="n">
-        <v>202967000</v>
+        <v>6790000</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Xiva Metall MChJ</t>
+          <t>Bunyodkor Mato MChJ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>297071667</t>
+          <t>243978194</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000210264664001</t>
+          <t>20208000261919541001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1071,14 +1071,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №33/26, НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №86/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09.07.2026</t>
+          <t>08.07.2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1088,31 +1088,31 @@
       </c>
       <c r="C23" s="2" t="n"/>
       <c r="D23" s="2" t="n">
-        <v>3742000</v>
+        <v>2955000</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Xiva Metall MChJ</t>
+          <t>Denov Moy MChJ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>297071667</t>
+          <t>335454567</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000210264664001</t>
+          <t>20208000523414352001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6023</t>
+          <t>Shartnoma №134/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
@@ -1127,40 +1127,40 @@
           <t>114</t>
         </is>
       </c>
-      <c r="C24" s="2" t="n">
-        <v>4442000</v>
-      </c>
-      <c r="D24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n">
+        <v>6095000</v>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Toshkent Qurilish Materiallari MChJ</t>
+          <t>Denov Moy MChJ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>378325139</t>
+          <t>335454567</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20208000064839218001</t>
+          <t>20208000523414352001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Ijara haqi iyul oyi uchun, shartn. №5/23</t>
+          <t>Оплата за товар по счет-фактуре №7036 от 09.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>09.07.2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1169,34 +1169,39 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>37100000</v>
+        <v>4442000</v>
       </c>
       <c r="D25" s="2" t="n"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-1541)</t>
+          <t>Oqtosh Qurilish AJ</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>242569188</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>16307000266463654417</t>
+          <t>20208000399873134001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-1541 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>Bino ijarasi uchun to'lo iyul</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>10.07.2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1206,38 +1211,38 @@
       </c>
       <c r="C26" s="2" t="n"/>
       <c r="D26" s="2" t="n">
-        <v>40471000</v>
+        <v>19584000</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Xiva Metall MChJ</t>
+          <t>Denov Moy MChJ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>297071667</t>
+          <t>335454567</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000210264664001</t>
+          <t>20208000523414352001</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №8457 за поставленный товар</t>
+          <t>Оплата за продукцию по договору №285/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>10.07.2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1247,38 +1252,38 @@
       </c>
       <c r="C27" s="2" t="n"/>
       <c r="D27" s="2" t="n">
-        <v>18801000</v>
+        <v>14637000</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Xiva Metall MChJ</t>
+          <t>Shodlik Poligraf AJ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>297071667</t>
+          <t>307166732</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000210264664001</t>
+          <t>20208000026466438001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Shartnoma №162/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за товар по договору №198/26 от 10.07.2026</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>10.07.2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1288,38 +1293,38 @@
       </c>
       <c r="C28" s="2" t="n"/>
       <c r="D28" s="2" t="n">
-        <v>8219000</v>
+        <v>6336000</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Xiva Metall MChJ</t>
+          <t>Denov Moy MChJ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>297071667</t>
+          <t>335454567</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20208000210264664001</t>
+          <t>20208000523414352001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Shartnoma №172/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата по с/ф №2812 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>10.07.2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1328,32 +1333,27 @@
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>15839000</v>
+        <v>37100000</v>
       </c>
       <c r="D29" s="2" t="n"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Nurafshon Non XK</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>243783821</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-1541)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20208000725266702001</t>
+          <t>16307000266463654417</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №67/26</t>
+          <t>Kredit shartnomasi L-2025-1541 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
     </row>
@@ -1368,33 +1368,33 @@
           <t>120</t>
         </is>
       </c>
-      <c r="C30" s="2" t="n">
-        <v>26068000</v>
-      </c>
-      <c r="D30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n">
+        <v>140572000</v>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Nurafshon Non XK</t>
+          <t>Bunyodkor Mato MChJ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>243783821</t>
+          <t>243978194</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20208000725266702001</t>
+          <t>20208000261919541001</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №1037</t>
+          <t>Оплата за товар по счет-фактуре №4258 от 13.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
@@ -1409,40 +1409,40 @@
           <t>121</t>
         </is>
       </c>
-      <c r="C31" s="2" t="n">
-        <v>71396000</v>
-      </c>
-      <c r="D31" s="2" t="n"/>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="n">
+        <v>33549000</v>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Mehnat Polimer XK</t>
+          <t>Shodlik Poligraf AJ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>203106510</t>
+          <t>307166732</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20208000866576450001</t>
+          <t>20208000026466438001</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №135/26</t>
+          <t>Shartnoma №35/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>15.07.2026</t>
+          <t>13.07.2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1452,38 +1452,38 @@
       </c>
       <c r="C32" s="2" t="n"/>
       <c r="D32" s="2" t="n">
-        <v>6857000</v>
+        <v>4090000</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Shahrisabz Polimer AJ</t>
+          <t>Shodlik Poligraf AJ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>307354545</t>
+          <t>307166732</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20208000745234143001</t>
+          <t>20208000026466438001</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5138</t>
+          <t>Оплата по счет-фактуре №9255 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>15.07.2026</t>
+          <t>13.07.2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1493,38 +1493,38 @@
       </c>
       <c r="C33" s="2" t="n"/>
       <c r="D33" s="2" t="n">
-        <v>5145000</v>
+        <v>3976000</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Xiva Metall MChJ</t>
+          <t>Shodlik Poligraf AJ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>297071667</t>
+          <t>307166732</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20208000210264664001</t>
+          <t>20208000026466438001</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №4221 15.07.2026, QQS bilan</t>
+          <t>Оплата за товар по с/ф №5132 от 13.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>15.07.2026</t>
+          <t>14.07.2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1532,40 +1532,40 @@
           <t>124</t>
         </is>
       </c>
-      <c r="C34" s="2" t="n">
-        <v>4558000</v>
-      </c>
-      <c r="D34" s="2" t="n"/>
+      <c r="C34" s="2" t="n"/>
+      <c r="D34" s="2" t="n">
+        <v>7482000</v>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Shodlik Poligraf AJ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>307166732</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000026466438001</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Iyun oyi uchun ijtimoiy soliq</t>
+          <t>Оплата за товар по счет-фактуре №7473 от 14.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>15.07.2026</t>
+          <t>14.07.2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1599,14 +1599,14 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Jismoniy shaxslar daromad solig'i iyun 2026</t>
+          <t>Социальный налог за июнь 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>16.07.2026</t>
+          <t>14.07.2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1614,40 +1614,40 @@
           <t>126</t>
         </is>
       </c>
-      <c r="C36" s="2" t="n"/>
-      <c r="D36" s="2" t="n">
-        <v>47334000</v>
-      </c>
+      <c r="C36" s="2" t="n">
+        <v>4558000</v>
+      </c>
+      <c r="D36" s="2" t="n"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Xiva Metall MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>297071667</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20208000210264664001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8092</t>
+          <t>НАЛОГ НА ДОХОДЫ ФИЗИЧЕСКИХ ЛИЦ ЗА ИЮНЬ 2026 Г.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>16.07.2026</t>
+          <t>14.07.2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1655,40 +1655,40 @@
           <t>127</t>
         </is>
       </c>
-      <c r="C37" s="2" t="n"/>
-      <c r="D37" s="2" t="n">
-        <v>2480000</v>
-      </c>
+      <c r="C37" s="2" t="n">
+        <v>165228000</v>
+      </c>
+      <c r="D37" s="2" t="n"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Xiva Metall MChJ</t>
+          <t>Nukus Logistik MChJ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>297071667</t>
+          <t>210651038</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20208000210264664001</t>
+          <t>20208000657645067001</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №2721</t>
+          <t>Предоплата за материалы по договору №2/26</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>16.07.2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1698,38 +1698,38 @@
       </c>
       <c r="C38" s="2" t="n"/>
       <c r="D38" s="2" t="n">
-        <v>5395000</v>
+        <v>7074000</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Xiva Metall MChJ</t>
+          <t>Shodlik Poligraf AJ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>297071667</t>
+          <t>307166732</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20208000210264664001</t>
+          <t>20208000026466438001</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8704</t>
+          <t>Оплата за товар по счет-фактуре №2291 от 16.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>16.07.2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1739,21 +1739,21 @@
       </c>
       <c r="C39" s="2" t="n"/>
       <c r="D39" s="2" t="n">
-        <v>2982000</v>
+        <v>5648000</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Xiva Metall MChJ</t>
+          <t>Bunyodkor Mato MChJ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>297071667</t>
+          <t>243978194</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20208000210264664001</t>
+          <t>20208000261919541001</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1763,14 +1763,14 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №218/26, QQS 12%</t>
+          <t>Оплата за товар по счет-фактуре №8143 от 16.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>16.07.2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1778,23 +1778,23 @@
           <t>130</t>
         </is>
       </c>
-      <c r="C40" s="2" t="n"/>
-      <c r="D40" s="2" t="n">
-        <v>2885000</v>
-      </c>
+      <c r="C40" s="2" t="n">
+        <v>30424000</v>
+      </c>
+      <c r="D40" s="2" t="n"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Shahrisabz Polimer AJ</t>
+          <t>Nukus Logistik MChJ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>307354545</t>
+          <t>210651038</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20208000745234143001</t>
+          <t>20208000657645067001</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -1804,14 +1804,14 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8862</t>
+          <t>Оплата за товары согласно с/ф №4389</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>17.07.2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1821,31 +1821,31 @@
       </c>
       <c r="C41" s="2" t="n"/>
       <c r="D41" s="2" t="n">
-        <v>15789000</v>
+        <v>6812000</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Shahrisabz Polimer AJ</t>
+          <t>Bunyodkor Mato MChJ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>307354545</t>
+          <t>243978194</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20208000745234143001</t>
+          <t>20208000261919541001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4291</t>
+          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №64/26 ОТ 17.07.2026</t>
         </is>
       </c>
     </row>
@@ -1862,31 +1862,31 @@
       </c>
       <c r="C42" s="2" t="n"/>
       <c r="D42" s="2" t="n">
-        <v>4974000</v>
+        <v>20964000</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Shahrisabz Polimer AJ</t>
+          <t>Shahrisabz Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>307354545</t>
+          <t>301266775</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20208000745234143001</t>
+          <t>20208000866099754001</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №160/26 от 20.07.2026</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №8967</t>
         </is>
       </c>
     </row>
@@ -1901,33 +1901,33 @@
           <t>133</t>
         </is>
       </c>
-      <c r="C43" s="2" t="n">
-        <v>14372000</v>
-      </c>
-      <c r="D43" s="2" t="n"/>
+      <c r="C43" s="2" t="n"/>
+      <c r="D43" s="2" t="n">
+        <v>9173000</v>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Mehnat Polimer XK</t>
+          <t>Shahrisabz Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>203106510</t>
+          <t>301266775</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20208000866576450001</t>
+          <t>20208000866099754001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №2903</t>
+          <t>Оплата за товар по счет-фактуре №7605 от 20.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
@@ -1943,39 +1943,39 @@
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>27687000</v>
+        <v>21113000</v>
       </c>
       <c r="D44" s="2" t="n"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ishonch Trans Servis XK</t>
+          <t>Lazzat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>352219763</t>
+          <t>286324779</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000492874273001</t>
+          <t>20208000110291460001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №112/26</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №253/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>21.07.2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1984,32 +1984,32 @@
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>65300000</v>
+        <v>7068000</v>
       </c>
       <c r="D45" s="2" t="n"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Mehnat Polimer XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>203106510</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000866576450001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №3/26</t>
+          <t>НДС за июнь 2026 г.</t>
         </is>
       </c>
     </row>
@@ -2024,40 +2024,40 @@
           <t>136</t>
         </is>
       </c>
-      <c r="C46" s="2" t="n"/>
-      <c r="D46" s="2" t="n">
-        <v>2276000</v>
-      </c>
+      <c r="C46" s="2" t="n">
+        <v>21570000</v>
+      </c>
+      <c r="D46" s="2" t="n"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Xiva Metall MChJ</t>
+          <t>Namangan Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>297071667</t>
+          <t>345844769</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20208000210264664001</t>
+          <t>20208000770866963001</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №148/26, QQS 12%</t>
+          <t>Предоплата за материалы по дог. №71/26</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>21.07.2026</t>
+          <t>22.07.2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2066,39 +2066,39 @@
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>7225000</v>
+        <v>18128000</v>
       </c>
       <c r="D47" s="2" t="n"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Nukus Logistik MChJ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>210651038</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000657645067001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>QQS iyun 2026 uchun</t>
+          <t>Trasport xizmatlari uchun to'lov, shartn. №76/26</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>22.07.2026</t>
+          <t>23.07.2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2108,38 +2108,38 @@
       </c>
       <c r="C48" s="2" t="n"/>
       <c r="D48" s="2" t="n">
-        <v>60078000</v>
+        <v>18615000</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Shahrisabz Polimer AJ</t>
+          <t>Denov Moy MChJ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>307354545</t>
+          <t>335454567</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20208000745234143001</t>
+          <t>20208000523414352001</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №152/26, QQS 12%</t>
+          <t>Оплата по счет-фактуре №3344 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>22.07.2026</t>
+          <t>23.07.2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2149,38 +2149,38 @@
       </c>
       <c r="C49" s="2" t="n"/>
       <c r="D49" s="2" t="n">
-        <v>12603000</v>
+        <v>7069000</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Xiva Metall MChJ</t>
+          <t>Ziyo Avto Savdo AJ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>297071667</t>
+          <t>213072228</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000210264664001</t>
+          <t>20208000697884713001</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №4200 от 22.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №2563 от 23.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>22.07.2026</t>
+          <t>23.07.2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2188,40 +2188,40 @@
           <t>140</t>
         </is>
       </c>
-      <c r="C50" s="2" t="n"/>
-      <c r="D50" s="2" t="n">
-        <v>3079000</v>
-      </c>
+      <c r="C50" s="2" t="n">
+        <v>33707000</v>
+      </c>
+      <c r="D50" s="2" t="n"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Xiva Metall MChJ</t>
+          <t>Nukus Logistik MChJ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>297071667</t>
+          <t>210651038</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000210264664001</t>
+          <t>20208000657645067001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №8831 от 22.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за сырье по дог. №59/26 от 23.07.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>22.07.2026</t>
+          <t>24.07.2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2229,23 +2229,23 @@
           <t>141</t>
         </is>
       </c>
-      <c r="C51" s="2" t="n">
-        <v>112450000</v>
-      </c>
-      <c r="D51" s="2" t="n"/>
+      <c r="C51" s="2" t="n"/>
+      <c r="D51" s="2" t="n">
+        <v>5126000</v>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Mehnat Polimer XK</t>
+          <t>Denov Moy MChJ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>203106510</t>
+          <t>335454567</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20208000866576450001</t>
+          <t>20208000523414352001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2255,14 +2255,14 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №33/26</t>
+          <t>Предоплата за товар по договору №217/26 от 24.07.2026</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>23.07.2026</t>
+          <t>24.07.2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2270,40 +2270,40 @@
           <t>142</t>
         </is>
       </c>
-      <c r="C52" s="2" t="n"/>
-      <c r="D52" s="2" t="n">
-        <v>2715000</v>
-      </c>
+      <c r="C52" s="2" t="n">
+        <v>58301000</v>
+      </c>
+      <c r="D52" s="2" t="n"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Xiva Metall MChJ</t>
+          <t>Lazzat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>297071667</t>
+          <t>286324779</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20208000210264664001</t>
+          <t>20208000110291460001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №1068 от 23.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за транспортные услуги по договору №267/26</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>23.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2311,40 +2311,40 @@
           <t>143</t>
         </is>
       </c>
-      <c r="C53" s="2" t="n">
-        <v>41574000</v>
-      </c>
-      <c r="D53" s="2" t="n"/>
+      <c r="C53" s="2" t="n"/>
+      <c r="D53" s="2" t="n">
+        <v>38199000</v>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Mehnat Polimer XK</t>
+          <t>Denov Logistik MChJ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>203106510</t>
+          <t>315866983</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20208000866576450001</t>
+          <t>20208000368618236001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №296/26</t>
+          <t>Оплата за товар по счет-фактуре №4892 от 27.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>24.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2354,38 +2354,38 @@
       </c>
       <c r="C54" s="2" t="n"/>
       <c r="D54" s="2" t="n">
-        <v>7026000</v>
+        <v>8240000</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Omad Oziq-ovqat Savdo AJ</t>
+          <t>Bunyodkor Mato MChJ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>215158669</t>
+          <t>243978194</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20208000383686182001</t>
+          <t>20208000261919541001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №270/26, QQS 12%</t>
+          <t>Оплата за продукцию по договору №200/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>24.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2409,24 +2409,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000464360672001</t>
+          <t>20208000962245549001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию за июль 2026 г.</t>
+          <t>Elektr energiyasi uchun to'lov</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>28.07.2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2436,38 +2436,38 @@
       </c>
       <c r="C56" s="2" t="n"/>
       <c r="D56" s="2" t="n">
-        <v>2671000</v>
+        <v>17573000</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Xiva Metall MChJ</t>
+          <t>Shodlik Poligraf AJ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>297071667</t>
+          <t>307166732</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000210264664001</t>
+          <t>20208000026466438001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №1382</t>
+          <t>Shartnoma №173/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>28.07.2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2475,33 +2475,33 @@
           <t>147</t>
         </is>
       </c>
-      <c r="C57" s="2" t="n">
-        <v>69830000</v>
-      </c>
-      <c r="D57" s="2" t="n"/>
+      <c r="C57" s="2" t="n"/>
+      <c r="D57" s="2" t="n">
+        <v>7671000</v>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Ishonch Trans Servis XK</t>
+          <t>Shodlik Poligraf AJ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>352219763</t>
+          <t>307166732</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000492874273001</t>
+          <t>20208000026466438001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №254/26, QQS bilan</t>
+          <t>Оплата за продукцию по договору №59/26, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -2518,38 +2518,38 @@
       </c>
       <c r="C58" s="2" t="n"/>
       <c r="D58" s="2" t="n">
-        <v>2648000</v>
+        <v>3867000</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Xiva Metall MChJ</t>
+          <t>Shodlik Poligraf AJ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>297071667</t>
+          <t>307166732</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000210264664001</t>
+          <t>20208000026466438001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №9822</t>
+          <t>Оплата за товар по счет-фактуре №4298 от 28.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>29.07.2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2559,38 +2559,38 @@
       </c>
       <c r="C59" s="2" t="n"/>
       <c r="D59" s="2" t="n">
-        <v>72562000</v>
+        <v>28930000</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Zarafshon Agro Servis MChJ</t>
+          <t>Shodlik Poligraf AJ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>241696413</t>
+          <t>307166732</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20208000326640606001</t>
+          <t>20208000026466438001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Shartnoma №54/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за продукцию по договору №47/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>29.07.2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2600,38 +2600,38 @@
       </c>
       <c r="C60" s="2" t="n"/>
       <c r="D60" s="2" t="n">
-        <v>3932000</v>
+        <v>8346000</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Xiva Metall MChJ</t>
+          <t>Denov Logistik MChJ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>297071667</t>
+          <t>315866983</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20208000210264664001</t>
+          <t>20208000368618236001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №5406 от 31.07.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за товар по договору №143/26 от 29.07.2026</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>29.07.2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2640,34 +2640,39 @@
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>300000</v>
+        <v>19145000</v>
       </c>
       <c r="D61" s="2" t="n"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Nukus Logistik MChJ</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>210651038</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000657645067001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Bank xizmati uchun komissiya</t>
+          <t>Оплата за сырье по договору №178/26 от 29.07.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>30.07.2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2677,38 +2682,38 @@
       </c>
       <c r="C62" s="2" t="n"/>
       <c r="D62" s="2" t="n">
-        <v>9801000</v>
+        <v>8468000</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Xiva Metall MChJ</t>
+          <t>Shodlik Poligraf AJ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>297071667</t>
+          <t>307166732</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000210264664001</t>
+          <t>20208000026466438001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №130/26, QQS 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №4967 30.07.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>30.07.2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2716,40 +2721,40 @@
           <t>153</t>
         </is>
       </c>
-      <c r="C63" s="2" t="n">
-        <v>4959000</v>
-      </c>
-      <c r="D63" s="2" t="n"/>
+      <c r="C63" s="2" t="n"/>
+      <c r="D63" s="2" t="n">
+        <v>5619000</v>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Urganch Meva-Sabzavot MChJ</t>
+          <t>Denov Moy MChJ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>341863247</t>
+          <t>335454567</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000901102914001</t>
+          <t>20208000523414352001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Materiallar uchun odindan to'lov, shartnoma №160/26</t>
+          <t>Предоплата за товар по договору №127/26 от 30.07.2026</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>04.08.2026</t>
+          <t>30.07.2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2757,40 +2762,40 @@
           <t>154</t>
         </is>
       </c>
-      <c r="C64" s="2" t="n"/>
-      <c r="D64" s="2" t="n">
-        <v>9511000</v>
-      </c>
+      <c r="C64" s="2" t="n">
+        <v>75416000</v>
+      </c>
+      <c r="D64" s="2" t="n"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Zarafshon Agro Servis MChJ</t>
+          <t>Nukus Logistik MChJ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>241696413</t>
+          <t>210651038</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>20208000326640606001</t>
+          <t>20208000657645067001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7715</t>
+          <t>Оплата за сырье по дог. №296/26 от 30.07.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>04.08.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2799,22 +2804,17 @@
         </is>
       </c>
       <c r="C65" s="2" t="n">
-        <v>10022000</v>
+        <v>300000</v>
       </c>
       <c r="D65" s="2" t="n"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Urganch Meva-Sabzavot MChJ</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>341863247</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>20208000901102914001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -2824,14 +2824,14 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №187/26</t>
+          <t>Hisob-kassa xizmati uchun haq</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>05.08.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2841,38 +2841,38 @@
       </c>
       <c r="C66" s="2" t="n"/>
       <c r="D66" s="2" t="n">
-        <v>31490000</v>
+        <v>8885000</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Xiva Metall MChJ</t>
+          <t>Denov Moy MChJ</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>297071667</t>
+          <t>335454567</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>20208000210264664001</t>
+          <t>20208000523414352001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №1877 от 05.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за продукцию по дог. №197/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>06.08.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2880,35 +2880,40 @@
           <t>157</t>
         </is>
       </c>
-      <c r="C67" s="2" t="n">
-        <v>34191000</v>
-      </c>
-      <c r="D67" s="2" t="n"/>
+      <c r="C67" s="2" t="n"/>
+      <c r="D67" s="2" t="n">
+        <v>7980000</v>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Ziyo Avto Savdo AJ</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>213072228</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000697884713001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Ish haqi to'lovi iyul 2026 (plastik kartalarga)</t>
+          <t>Оплата по счет-фактуре №4346 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>06.08.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2916,40 +2921,40 @@
           <t>158</t>
         </is>
       </c>
-      <c r="C68" s="2" t="n">
-        <v>37963000</v>
-      </c>
-      <c r="D68" s="2" t="n"/>
+      <c r="C68" s="2" t="n"/>
+      <c r="D68" s="2" t="n">
+        <v>5330000</v>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Saodat Avto Savdo MChJ</t>
+          <t>Farovon Sut MChJ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>379177352</t>
+          <t>269641343</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20208000064880075001</t>
+          <t>20208000664060678001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №8057</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №150/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2957,23 +2962,23 @@
           <t>159</t>
         </is>
       </c>
-      <c r="C69" s="2" t="n">
-        <v>4543000</v>
-      </c>
-      <c r="D69" s="2" t="n"/>
+      <c r="C69" s="2" t="n"/>
+      <c r="D69" s="2" t="n">
+        <v>3751000</v>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Toshkent Qurilish Materiallari MChJ</t>
+          <t>Shodlik Poligraf AJ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>378325139</t>
+          <t>307166732</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20208000064839218001</t>
+          <t>20208000026466438001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -2983,14 +2988,14 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Ijara haqi avgust oyi uchun, shartnoma №5/23</t>
+          <t>Оплата по с/ф №8220 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>04.08.2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2998,40 +3003,40 @@
           <t>160</t>
         </is>
       </c>
-      <c r="C70" s="2" t="n">
-        <v>24736000</v>
-      </c>
-      <c r="D70" s="2" t="n"/>
+      <c r="C70" s="2" t="n"/>
+      <c r="D70" s="2" t="n">
+        <v>90656000</v>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Ishonch Trans Servis XK</t>
+          <t>Shodlik Poligraf AJ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>352219763</t>
+          <t>307166732</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20208000492874273001</t>
+          <t>20208000026466438001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №247/26, QQS bilan</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №9792</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>04.08.2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3041,38 +3046,38 @@
       </c>
       <c r="C71" s="2" t="n"/>
       <c r="D71" s="2" t="n">
-        <v>9334000</v>
+        <v>4266000</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Xiva Metall MChJ</t>
+          <t>Denov Moy MChJ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>297071667</t>
+          <t>335454567</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>20208000210264664001</t>
+          <t>20208000523414352001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №22/26, QQS 12%</t>
+          <t>Оплата за продукцию по дог. №156/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>04.08.2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3080,40 +3085,35 @@
           <t>162</t>
         </is>
       </c>
-      <c r="C72" s="2" t="n"/>
-      <c r="D72" s="2" t="n">
-        <v>5495000</v>
-      </c>
+      <c r="C72" s="2" t="n">
+        <v>34191000</v>
+      </c>
+      <c r="D72" s="2" t="n"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Shahrisabz Polimer AJ</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>307354545</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000745234143001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №181/26, QQS 12%</t>
+          <t>Заработная плата за июль 2026 г. (перечисление на пластиковые карты)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>05.08.2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3122,39 +3122,39 @@
         </is>
       </c>
       <c r="C73" s="2" t="n">
-        <v>32822000</v>
+        <v>44732000</v>
       </c>
       <c r="D73" s="2" t="n"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Mehnat Polimer XK</t>
+          <t>Yangi Hayot Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>203106510</t>
+          <t>365775229</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000866576450001</t>
+          <t>20208000558842472001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №1375</t>
+          <t>Оплата за упаковочные материалы, с/ф №8048</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>06.08.2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3162,35 +3162,40 @@
           <t>164</t>
         </is>
       </c>
-      <c r="C74" s="2" t="n">
-        <v>37100000</v>
-      </c>
-      <c r="D74" s="2" t="n"/>
+      <c r="C74" s="2" t="n"/>
+      <c r="D74" s="2" t="n">
+        <v>18026000</v>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-1541)</t>
+          <t>Denov Moy MChJ</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>335454567</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>16307000266463654417</t>
+          <t>20208000523414352001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-1541 bo'yicha navbatdagi to'lov (08.2026)</t>
+          <t>Оплата по счет-фактуре №4211 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>11.08.2026</t>
+          <t>06.08.2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3200,38 +3205,38 @@
       </c>
       <c r="C75" s="2" t="n"/>
       <c r="D75" s="2" t="n">
-        <v>6364000</v>
+        <v>6223000</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Xiva Metall MChJ</t>
+          <t>Denov Moy MChJ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>297071667</t>
+          <t>335454567</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>20208000210264664001</t>
+          <t>20208000523414352001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №89/26 от 11.08.2026</t>
+          <t>Оплата за товар по с/ф №6037 от 06.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>12.08.2026</t>
+          <t>06.08.2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3241,38 +3246,38 @@
       </c>
       <c r="C76" s="2" t="n"/>
       <c r="D76" s="2" t="n">
-        <v>45614000</v>
+        <v>4551000</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Xiva Metall MChJ</t>
+          <t>Shodlik Poligraf AJ</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>297071667</t>
+          <t>307166732</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>20208000210264664001</t>
+          <t>20208000026466438001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №84/26, QQS 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №7373 06.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>13.08.2026</t>
+          <t>06.08.2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3282,38 +3287,38 @@
       </c>
       <c r="C77" s="2" t="n"/>
       <c r="D77" s="2" t="n">
-        <v>4444000</v>
+        <v>3304000</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Xiva Metall MChJ</t>
+          <t>Shodlik Poligraf AJ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>297071667</t>
+          <t>307166732</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>20208000210264664001</t>
+          <t>20208000026466438001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №2230</t>
+          <t>Оплата за продукцию по договору №255/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>14.08.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3323,38 +3328,38 @@
       </c>
       <c r="C78" s="2" t="n"/>
       <c r="D78" s="2" t="n">
-        <v>309769000</v>
+        <v>45523000</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Zarafshon Agro Servis MChJ</t>
+          <t>Shahrisabz Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>241696413</t>
+          <t>301266775</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>20208000326640606001</t>
+          <t>20208000866099754001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №4532 14.08.2026, QQS bilan</t>
+          <t>Предоплата за товар по договору №287/26 от 07.08.2026</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>14.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3362,40 +3367,40 @@
           <t>169</t>
         </is>
       </c>
-      <c r="C79" s="2" t="n">
-        <v>4662000</v>
-      </c>
-      <c r="D79" s="2" t="n"/>
+      <c r="C79" s="2" t="n"/>
+      <c r="D79" s="2" t="n">
+        <v>29283000</v>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Shahrisabz Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>301266775</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000866099754001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Iyul oyi uchun ijtimoiy soliq</t>
+          <t>Оплата за продукцию по дог. №73/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>14.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3403,40 +3408,40 @@
           <t>170</t>
         </is>
       </c>
-      <c r="C80" s="2" t="n">
-        <v>4662000</v>
-      </c>
-      <c r="D80" s="2" t="n"/>
+      <c r="C80" s="2" t="n"/>
+      <c r="D80" s="2" t="n">
+        <v>11193000</v>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Denov Moy MChJ</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>335454567</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000523414352001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Jismoniy shaxslar daromad solig'i iyul 2026</t>
+          <t>Оплата за продукцию по дог. №166/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>18.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3446,38 +3451,38 @@
       </c>
       <c r="C81" s="2" t="n"/>
       <c r="D81" s="2" t="n">
-        <v>4729000</v>
+        <v>10739000</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Shahrisabz Polimer AJ</t>
+          <t>Shodlik Poligraf AJ</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>307354545</t>
+          <t>307166732</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>20208000745234143001</t>
+          <t>20208000026466438001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №57/26, НДС 12%</t>
+          <t>Оплата за продукцию по договору №9/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>18.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3485,40 +3490,40 @@
           <t>172</t>
         </is>
       </c>
-      <c r="C82" s="2" t="n">
-        <v>20533000</v>
-      </c>
-      <c r="D82" s="2" t="n"/>
+      <c r="C82" s="2" t="n"/>
+      <c r="D82" s="2" t="n">
+        <v>5020000</v>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Urganch Meva-Sabzavot MChJ</t>
+          <t>Shodlik Poligraf AJ</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>341863247</t>
+          <t>307166732</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20208000901102914001</t>
+          <t>20208000026466438001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №66/26, QQS bilan</t>
+          <t>Оплата по счет-фактуре №5583 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>20.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3526,40 +3531,40 @@
           <t>173</t>
         </is>
       </c>
-      <c r="C83" s="2" t="n"/>
-      <c r="D83" s="2" t="n">
-        <v>9145000</v>
-      </c>
+      <c r="C83" s="2" t="n">
+        <v>4543000</v>
+      </c>
+      <c r="D83" s="2" t="n"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Xiva Metall MChJ</t>
+          <t>Oqtosh Qurilish AJ</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>297071667</t>
+          <t>242569188</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000210264664001</t>
+          <t>20208000399873134001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №257/26 от 20.08.2026</t>
+          <t>Ijara haqi avgust oyi uchun, shartnoma №5/24</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>20.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3568,39 +3573,34 @@
         </is>
       </c>
       <c r="C84" s="2" t="n">
-        <v>63505000</v>
+        <v>37100000</v>
       </c>
       <c r="D84" s="2" t="n"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Mehnat Polimer XK</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>203106510</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-1541)</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>20208000866576450001</t>
+          <t>16307000266463654417</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №225/26</t>
+          <t>Kredit shartnomasi L-2025-1541 bo'yicha navbatdagi to'lov (08.2026)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>12.08.2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3610,38 +3610,38 @@
       </c>
       <c r="C85" s="2" t="n"/>
       <c r="D85" s="2" t="n">
-        <v>12407000</v>
+        <v>7148000</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Xiva Metall MChJ</t>
+          <t>Denov Moy MChJ</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>297071667</t>
+          <t>335454567</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>20208000210264664001</t>
+          <t>20208000523414352001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8975</t>
+          <t>Оплата за продукцию по дог. №176/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>12.08.2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,23 +3649,23 @@
           <t>176</t>
         </is>
       </c>
-      <c r="C86" s="2" t="n"/>
-      <c r="D86" s="2" t="n">
-        <v>10089000</v>
-      </c>
+      <c r="C86" s="2" t="n">
+        <v>12006000</v>
+      </c>
+      <c r="D86" s="2" t="n"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Shahrisabz Polimer AJ</t>
+          <t>Nukus Logistik MChJ</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>307354545</t>
+          <t>210651038</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20208000745234143001</t>
+          <t>20208000657645067001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -3675,14 +3675,14 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №7466 21.08.2026, QQS bilan</t>
+          <t>Оплата за товары согласно счет-фактуре №4543</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>13.08.2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3692,38 +3692,38 @@
       </c>
       <c r="C87" s="2" t="n"/>
       <c r="D87" s="2" t="n">
-        <v>4704000</v>
+        <v>9466000</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Shahrisabz Polimer AJ</t>
+          <t>Shodlik Poligraf AJ</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>307354545</t>
+          <t>307166732</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20208000745234143001</t>
+          <t>20208000026466438001</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №5361 21.08.2026, QQS bilan</t>
+          <t>Предоплата за товар по договору №212/26 от 13.08.2026</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3731,40 +3731,40 @@
           <t>178</t>
         </is>
       </c>
-      <c r="C88" s="2" t="n">
-        <v>7851000</v>
-      </c>
-      <c r="D88" s="2" t="n"/>
+      <c r="C88" s="2" t="n"/>
+      <c r="D88" s="2" t="n">
+        <v>31175000</v>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Shodlik Poligraf AJ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>307166732</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000026466438001</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>QQS IYUL 2026 UCHUN</t>
+          <t>Оплата за товар по с/ф №730 от 14.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3772,40 +3772,40 @@
           <t>179</t>
         </is>
       </c>
-      <c r="C89" s="2" t="n"/>
-      <c r="D89" s="2" t="n">
-        <v>33907000</v>
-      </c>
+      <c r="C89" s="2" t="n">
+        <v>20626000</v>
+      </c>
+      <c r="D89" s="2" t="n"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Xiva Metall MChJ</t>
+          <t>Lazzat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>297071667</t>
+          <t>286324779</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>20208000210264664001</t>
+          <t>20208000110291460001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Shartnoma №271/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за сырье по договору №148/26 от 14.08.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3813,40 +3813,40 @@
           <t>180</t>
         </is>
       </c>
-      <c r="C90" s="2" t="n"/>
-      <c r="D90" s="2" t="n">
-        <v>5113000</v>
-      </c>
+      <c r="C90" s="2" t="n">
+        <v>29405000</v>
+      </c>
+      <c r="D90" s="2" t="n"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Xiva Metall MChJ</t>
+          <t>Namangan Non XK</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>297071667</t>
+          <t>203301054</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20208000210264664001</t>
+          <t>20208000769946250001</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №1415 от 24.08.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за материалы по договору №239/26</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3854,40 +3854,40 @@
           <t>181</t>
         </is>
       </c>
-      <c r="C91" s="2" t="n">
-        <v>2839000</v>
-      </c>
-      <c r="D91" s="2" t="n"/>
+      <c r="C91" s="2" t="n"/>
+      <c r="D91" s="2" t="n">
+        <v>20245000</v>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Shodlik Poligraf AJ</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>307166732</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20208000464360672001</t>
+          <t>20208000026466438001</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov</t>
+          <t>Оплата за продукцию по договору №88/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3895,23 +3895,23 @@
           <t>182</t>
         </is>
       </c>
-      <c r="C92" s="2" t="n">
-        <v>7661000</v>
-      </c>
-      <c r="D92" s="2" t="n"/>
+      <c r="C92" s="2" t="n"/>
+      <c r="D92" s="2" t="n">
+        <v>15161000</v>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Mehnat Polimer XK</t>
+          <t>Denov Moy MChJ</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>203106510</t>
+          <t>335454567</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20208000866576450001</t>
+          <t>20208000523414352001</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -3921,14 +3921,14 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №119/26</t>
+          <t>Оплата за товар по счет-фактуре №9988 от 17.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3936,23 +3936,23 @@
           <t>183</t>
         </is>
       </c>
-      <c r="C93" s="2" t="n">
-        <v>8566000</v>
-      </c>
-      <c r="D93" s="2" t="n"/>
+      <c r="C93" s="2" t="n"/>
+      <c r="D93" s="2" t="n">
+        <v>10714000</v>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Urganch Meva-Sabzavot MChJ</t>
+          <t>Shahrisabz Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>341863247</t>
+          <t>301266775</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>20208000901102914001</t>
+          <t>20208000866099754001</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -3962,14 +3962,14 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №71/26, QQS bilan</t>
+          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №6896 ОТ 17.08.2026, В Т.Ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3979,38 +3979,38 @@
       </c>
       <c r="C94" s="2" t="n"/>
       <c r="D94" s="2" t="n">
-        <v>12580000</v>
+        <v>7037000</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Ilhom Sut MChJ</t>
+          <t>Denov Moy MChJ</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>204439781</t>
+          <t>335454567</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>20208000422619195001</t>
+          <t>20208000523414352001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №284/26, QQS 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №7506 17.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4018,40 +4018,40 @@
           <t>185</t>
         </is>
       </c>
-      <c r="C95" s="2" t="n">
-        <v>5263000</v>
-      </c>
-      <c r="D95" s="2" t="n"/>
+      <c r="C95" s="2" t="n"/>
+      <c r="D95" s="2" t="n">
+        <v>6070000</v>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Saodat Avto Savdo MChJ</t>
+          <t>Oqtosh Plastik MChJ</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>379177352</t>
+          <t>382254774</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>20208000064880075001</t>
+          <t>20208000422149307001</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №121/26</t>
+          <t>Предоплата затовар по договору №236/26 от 17.08.2026</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4059,23 +4059,23 @@
           <t>186</t>
         </is>
       </c>
-      <c r="C96" s="2" t="n">
-        <v>17693000</v>
-      </c>
-      <c r="D96" s="2" t="n"/>
+      <c r="C96" s="2" t="n"/>
+      <c r="D96" s="2" t="n">
+        <v>4645000</v>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Urganch Meva-Sabzavot MChJ</t>
+          <t>Navoiy Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>341863247</t>
+          <t>359568178</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>20208000901102914001</t>
+          <t>20208000926299217001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4085,14 +4085,14 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №35/26</t>
+          <t>Оплата за товар по счет-фактуре №3973 от 17.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>26.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4101,39 +4101,39 @@
         </is>
       </c>
       <c r="C97" s="2" t="n">
-        <v>19411000</v>
+        <v>4662000</v>
       </c>
       <c r="D97" s="2" t="n"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Mehnat Polimer XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>203106510</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>20208000866576450001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №90/26</t>
+          <t>Социальный налог за июль 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>27.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4142,39 +4142,39 @@
         </is>
       </c>
       <c r="C98" s="2" t="n">
-        <v>21164000</v>
+        <v>4662000</v>
       </c>
       <c r="D98" s="2" t="n"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Saodat Avto Savdo MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>379177352</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20208000064880075001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №213/26</t>
+          <t>НДФЛ за июль 2026</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>27.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4183,39 +4183,39 @@
         </is>
       </c>
       <c r="C99" s="2" t="n">
-        <v>29071000</v>
+        <v>54894000</v>
       </c>
       <c r="D99" s="2" t="n"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Urganch Meva-Sabzavot MChJ</t>
+          <t>Chirchiq Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>341863247</t>
+          <t>221976374</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20208000901102914001</t>
+          <t>20208000287427310001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №126/26</t>
+          <t>Оплата за упаковочные материалы, с/ф №9837</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>28.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4225,38 +4225,38 @@
       </c>
       <c r="C100" s="2" t="n"/>
       <c r="D100" s="2" t="n">
-        <v>107668000</v>
+        <v>3787000</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Termiz Mebel MChJ</t>
+          <t>Shodlik Poligraf AJ</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>209822547</t>
+          <t>307166732</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000404221493001</t>
+          <t>20208000026466438001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №215/26, QQS 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №8907</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>28.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4266,38 +4266,38 @@
       </c>
       <c r="C101" s="2" t="n"/>
       <c r="D101" s="2" t="n">
-        <v>8148000</v>
+        <v>3332000</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Xiva Metall MChJ</t>
+          <t>Denov Moy MChJ</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>297071667</t>
+          <t>335454567</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000210264664001</t>
+          <t>20208000523414352001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №133/26 от 28.08.2026</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №139/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4307,38 +4307,38 @@
       </c>
       <c r="C102" s="2" t="n"/>
       <c r="D102" s="2" t="n">
-        <v>9075000</v>
+        <v>16050000</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Xiva Metall MChJ</t>
+          <t>Shodlik Poligraf AJ</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>297071667</t>
+          <t>307166732</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20208000210264664001</t>
+          <t>20208000026466438001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №3826</t>
+          <t>Предоплата за товар по договору №35/26 от 20.08.2026</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4348,38 +4348,38 @@
       </c>
       <c r="C103" s="2" t="n"/>
       <c r="D103" s="2" t="n">
-        <v>4881000</v>
+        <v>12166000</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Xiva Metall MChJ</t>
+          <t>Denov Moy MChJ</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>297071667</t>
+          <t>335454567</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>20208000210264664001</t>
+          <t>20208000523414352001</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №2081</t>
+          <t>Оплата за товар по счет-фактуре №1174 от 20.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4388,34 +4388,39 @@
         </is>
       </c>
       <c r="C104" s="2" t="n">
-        <v>300000</v>
+        <v>13879000</v>
       </c>
       <c r="D104" s="2" t="n"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Namangan Non XK</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>203301054</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000769946250001</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>HISOB-KASSA XIZMATI UCHUN HAQ</t>
+          <t>Оплата за сырье по договору №83/26 от 20.08.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4424,39 +4429,39 @@
         </is>
       </c>
       <c r="C105" s="2" t="n">
-        <v>7826000</v>
+        <v>42188000</v>
       </c>
       <c r="D105" s="2" t="n"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Ishonch Trans Servis XK</t>
+          <t>Yangi Hayot Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>352219763</t>
+          <t>365775229</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000492874273001</t>
+          <t>20208000558842472001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №221/26</t>
+          <t>Tovarlar uchu to'lov h/f №9398</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4464,40 +4469,40 @@
           <t>196</t>
         </is>
       </c>
-      <c r="C106" s="2" t="n">
-        <v>7912000</v>
-      </c>
-      <c r="D106" s="2" t="n"/>
+      <c r="C106" s="2" t="n"/>
+      <c r="D106" s="2" t="n">
+        <v>21137000</v>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Saodat Avto Savdo MChJ</t>
+          <t>Shodlik Poligraf AJ</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>379177352</t>
+          <t>307166732</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20208000064880075001</t>
+          <t>20208000026466438001</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №181/26</t>
+          <t>Оплата по счет-фактуре №7115 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4505,23 +4510,23 @@
           <t>197</t>
         </is>
       </c>
-      <c r="C107" s="2" t="n">
-        <v>209286000</v>
-      </c>
-      <c r="D107" s="2" t="n"/>
+      <c r="C107" s="2" t="n"/>
+      <c r="D107" s="2" t="n">
+        <v>21084000</v>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Mehnat Polimer XK</t>
+          <t>Denov Moy MChJ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>203106510</t>
+          <t>335454567</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20208000866576450001</t>
+          <t>20208000523414352001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -4531,14 +4536,14 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №203/26</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №9962</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>01.09.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4548,38 +4553,38 @@
       </c>
       <c r="C108" s="2" t="n"/>
       <c r="D108" s="2" t="n">
-        <v>35251000</v>
+        <v>11241000</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Shahrisabz Polimer AJ</t>
+          <t>Bunyodkor Mato MChJ</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>307354545</t>
+          <t>243978194</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>20208000745234143001</t>
+          <t>20208000261919541001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5244</t>
+          <t>Tovar uchun to'lov, hisob-faktura №756 21.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>01.09.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4589,38 +4594,38 @@
       </c>
       <c r="C109" s="2" t="n"/>
       <c r="D109" s="2" t="n">
-        <v>5761000</v>
+        <v>4888000</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Xiva Metall MChJ</t>
+          <t>Shodlik Poligraf AJ</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>297071667</t>
+          <t>307166732</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>20208000210264664001</t>
+          <t>20208000026466438001</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №164/26, QQS 12%</t>
+          <t>Предоплата за товар по дог. №92/26 от 21.08.2026</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>01.09.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4629,39 +4634,39 @@
         </is>
       </c>
       <c r="C110" s="2" t="n">
-        <v>209222000</v>
+        <v>7802000</v>
       </c>
       <c r="D110" s="2" t="n"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Urganch Meva-Sabzavot MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>341863247</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>20208000901102914001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №84/26, QQS bilan</t>
+          <t>НДС за июль 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>02.09.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4671,38 +4676,38 @@
       </c>
       <c r="C111" s="2" t="n"/>
       <c r="D111" s="2" t="n">
-        <v>21457000</v>
+        <v>51759000</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Xiva Metall MChJ</t>
+          <t>Shahrisabz Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>297071667</t>
+          <t>301266775</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>20208000210264664001</t>
+          <t>20208000866099754001</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №6435 02.09.2026, QQS bilan</t>
+          <t>Оплата за продукцию по договору №265/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4712,38 +4717,38 @@
       </c>
       <c r="C112" s="2" t="n"/>
       <c r="D112" s="2" t="n">
-        <v>4847000</v>
+        <v>40011000</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Xiva Metall MChJ</t>
+          <t>Shodlik Poligraf AJ</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>297071667</t>
+          <t>307166732</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>20208000210264664001</t>
+          <t>20208000026466438001</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №526 04.09.2026, QQS bilan</t>
+          <t>Оплата по с/ф №708 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4753,38 +4758,38 @@
       </c>
       <c r="C113" s="2" t="n"/>
       <c r="D113" s="2" t="n">
-        <v>3544000</v>
+        <v>26842000</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Sarbon Yog'och XK</t>
+          <t>Shodlik Poligraf AJ</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>309595681</t>
+          <t>307166732</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000879262992001</t>
+          <t>20208000026466438001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Shartnoma №244/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата по счет-фактуре №8306 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4793,34 +4798,39 @@
         </is>
       </c>
       <c r="C114" s="2" t="n">
-        <v>37177000</v>
+        <v>35772000</v>
       </c>
       <c r="D114" s="2" t="n"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Yulduz Qog'oz XK</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>317735260</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000488007556001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Заработная плата за август 2026 г. (перечисление на пластиковые карты)</t>
+          <t>Оплата за транспортные услуги по договору №299/26</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>08.09.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4829,39 +4839,39 @@
         </is>
       </c>
       <c r="C115" s="2" t="n">
-        <v>4940000</v>
+        <v>16648000</v>
       </c>
       <c r="D115" s="2" t="n"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Toshkent Qurilish Materiallari MChJ</t>
+          <t>Nukus Logistik MChJ</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>378325139</t>
+          <t>210651038</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>20208000064839218001</t>
+          <t>20208000657645067001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>BINO IJARASI UCHUN TO'LOV SENTYABR</t>
+          <t>Предоплата за материалы по договору №107/26</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>10.09.2026</t>
+          <t>26.08.2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4871,38 +4881,38 @@
       </c>
       <c r="C116" s="2" t="n"/>
       <c r="D116" s="2" t="n">
-        <v>4218000</v>
+        <v>34849000</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Xiva Metall MChJ</t>
+          <t>Oqtosh Plastik MChJ</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>297071667</t>
+          <t>382254774</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20208000210264664001</t>
+          <t>20208000422149307001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №1804</t>
+          <t>Предоплата за товар по договору №197/26 от 26.08.2026</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>10.09.2026</t>
+          <t>26.08.2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4910,40 +4920,40 @@
           <t>207</t>
         </is>
       </c>
-      <c r="C117" s="2" t="n">
-        <v>32426000</v>
-      </c>
-      <c r="D117" s="2" t="n"/>
+      <c r="C117" s="2" t="n"/>
+      <c r="D117" s="2" t="n">
+        <v>6925000</v>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Mehnat Polimer XK</t>
+          <t>Shodlik Poligraf AJ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>203106510</t>
+          <t>307166732</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000866576450001</t>
+          <t>20208000026466438001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Transport xizmatlri uchun to'lov, shartnoma №24/26</t>
+          <t>Оплата за продукцию по договору №27/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>10.09.2026</t>
+          <t>27.08.2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4952,34 +4962,39 @@
         </is>
       </c>
       <c r="C118" s="2" t="n">
-        <v>37100000</v>
+        <v>2839000</v>
       </c>
       <c r="D118" s="2" t="n"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-1541)</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>16307000266463654417</t>
+          <t>20208000962245549001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-1541 bo'yicha navbatdagi to'lov (09.2026)</t>
+          <t>Оплата за электроэнергию согласно счету</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>11.09.2026</t>
+          <t>28.08.2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4989,38 +5004,38 @@
       </c>
       <c r="C119" s="2" t="n"/>
       <c r="D119" s="2" t="n">
-        <v>10782000</v>
+        <v>8800000</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Xiva Metall MChJ</t>
+          <t>Shodlik Poligraf AJ</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>297071667</t>
+          <t>307166732</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000210264664001</t>
+          <t>20208000026466438001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №108/26, QQS 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №2631 28.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>11.09.2026</t>
+          <t>28.08.2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5030,38 +5045,38 @@
       </c>
       <c r="C120" s="2" t="n"/>
       <c r="D120" s="2" t="n">
-        <v>7478000</v>
+        <v>8395000</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Omad Oziq-ovqat Savdo AJ</t>
+          <t>Shodlik Poligraf AJ</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>215158669</t>
+          <t>307166732</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>20208000383686182001</t>
+          <t>20208000026466438001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №238/26 от 11.09.2026</t>
+          <t>Оплата за продукцию по дог. №31/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>11.09.2026</t>
+          <t>28.08.2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5069,40 +5084,40 @@
           <t>211</t>
         </is>
       </c>
-      <c r="C121" s="2" t="n"/>
-      <c r="D121" s="2" t="n">
-        <v>3442000</v>
-      </c>
+      <c r="C121" s="2" t="n">
+        <v>56553000</v>
+      </c>
+      <c r="D121" s="2" t="n"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Gulshan Meva-Sabzavot AJ</t>
+          <t>Chirchiq Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>368012667</t>
+          <t>221976374</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>20208000578660997001</t>
+          <t>20208000287427310001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №130/26, НДС 12%</t>
+          <t>Оплата за транспортные услуги по договору №171/26</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>11.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5110,40 +5125,40 @@
           <t>212</t>
         </is>
       </c>
-      <c r="C122" s="2" t="n">
-        <v>15220000</v>
-      </c>
-      <c r="D122" s="2" t="n"/>
+      <c r="C122" s="2" t="n"/>
+      <c r="D122" s="2" t="n">
+        <v>6959000</v>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Barakali Agro MChJ</t>
+          <t>Farovon Sut MChJ</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>336458447</t>
+          <t>269641343</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000967708669001</t>
+          <t>20208000664060678001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №39/26, QQS bilan</t>
+          <t>Оплата за продукцию по договору №248/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5153,38 +5168,38 @@
       </c>
       <c r="C123" s="2" t="n"/>
       <c r="D123" s="2" t="n">
-        <v>153912000</v>
+        <v>5516000</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Ilhom Sut MChJ</t>
+          <t>Bunyodkor Mato MChJ</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>204439781</t>
+          <t>243978194</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>20208000422619195001</t>
+          <t>20208000261919541001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №239/26, QQS 12%</t>
+          <t>Оплата за продукцию по договору №72/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5192,40 +5207,35 @@
           <t>214</t>
         </is>
       </c>
-      <c r="C124" s="2" t="n"/>
-      <c r="D124" s="2" t="n">
-        <v>100018000</v>
-      </c>
+      <c r="C124" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D124" s="2" t="n"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Xiva Metall MChJ</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>297071667</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>20208000210264664001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №265/26, QQS 12%</t>
+          <t>Комиссия банка за расчетно-кассовое обслуживание за август</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5233,40 +5243,40 @@
           <t>215</t>
         </is>
       </c>
-      <c r="C125" s="2" t="n"/>
-      <c r="D125" s="2" t="n">
-        <v>6990000</v>
-      </c>
+      <c r="C125" s="2" t="n">
+        <v>11543000</v>
+      </c>
+      <c r="D125" s="2" t="n"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Marg'ilon Trans Servis MChJ</t>
+          <t>Lazzat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>384130722</t>
+          <t>286324779</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>20208000896978847001</t>
+          <t>20208000110291460001</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №2897</t>
+          <t>Transport xizmatlari uchun to'lov, shartn. №70/26</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5274,23 +5284,23 @@
           <t>216</t>
         </is>
       </c>
-      <c r="C126" s="2" t="n"/>
-      <c r="D126" s="2" t="n">
-        <v>6601000</v>
-      </c>
+      <c r="C126" s="2" t="n">
+        <v>15020000</v>
+      </c>
+      <c r="D126" s="2" t="n"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Shahrisabz Polimer AJ</t>
+          <t>Nukus Logistik MChJ</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>307354545</t>
+          <t>210651038</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>20208000745234143001</t>
+          <t>20208000657645067001</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -5300,14 +5310,14 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №4495 14.09.2026, QQS bilan</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №204/26</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5315,23 +5325,23 @@
           <t>217</t>
         </is>
       </c>
-      <c r="C127" s="2" t="n"/>
-      <c r="D127" s="2" t="n">
-        <v>5602000</v>
-      </c>
+      <c r="C127" s="2" t="n">
+        <v>170434000</v>
+      </c>
+      <c r="D127" s="2" t="n"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Shahrisabz Polimer AJ</t>
+          <t>Nukus Logistik MChJ</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>307354545</t>
+          <t>210651038</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000745234143001</t>
+          <t>20208000657645067001</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -5341,14 +5351,14 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №8694 14.09.2026, QQS bilan</t>
+          <t>Предоплата за материалы по договору №162/26</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>15.09.2026</t>
+          <t>01.09.2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5356,40 +5366,40 @@
           <t>218</t>
         </is>
       </c>
-      <c r="C128" s="2" t="n">
-        <v>5070000</v>
-      </c>
-      <c r="D128" s="2" t="n"/>
+      <c r="C128" s="2" t="n"/>
+      <c r="D128" s="2" t="n">
+        <v>11909000</v>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Bunyodkor Mato MChJ</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>243978194</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000261919541001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Ijtimoiy soliq avgust 2026</t>
+          <t>Предоплата за товар по договору №214/26 от 01.09.2026</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>15.09.2026</t>
+          <t>01.09.2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5397,40 +5407,40 @@
           <t>219</t>
         </is>
       </c>
-      <c r="C129" s="2" t="n">
-        <v>5070000</v>
-      </c>
-      <c r="D129" s="2" t="n"/>
+      <c r="C129" s="2" t="n"/>
+      <c r="D129" s="2" t="n">
+        <v>5591000</v>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Shodlik Poligraf AJ</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>307166732</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000026466438001</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>JISMONIY SHAXSLAR DAROMAD SOLIG'I AVGUST 2026</t>
+          <t>Предоплата за товар по договору №143/26 от 01.09.2026</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>15.09.2026</t>
+          <t>02.09.2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5439,39 +5449,39 @@
         </is>
       </c>
       <c r="C130" s="2" t="n">
-        <v>12218000</v>
+        <v>22720000</v>
       </c>
       <c r="D130" s="2" t="n"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Mehnat Polimer XK</t>
+          <t>Angren Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>203106510</t>
+          <t>328433928</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20208000866576450001</t>
+          <t>20208000706941050001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №284/26 от 15.09.2026, НДС 12%</t>
+          <t>Оплата за товары согласно с/ф №5820</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>16.09.2026</t>
+          <t>03.09.2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5481,38 +5491,38 @@
       </c>
       <c r="C131" s="2" t="n"/>
       <c r="D131" s="2" t="n">
-        <v>5965000</v>
+        <v>16375000</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Shahrisabz Polimer AJ</t>
+          <t>Shodlik Poligraf AJ</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>307354545</t>
+          <t>307166732</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20208000745234143001</t>
+          <t>20208000026466438001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Shartnoma №123/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата по с/ф №7017 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>17.09.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5522,38 +5532,38 @@
       </c>
       <c r="C132" s="2" t="n"/>
       <c r="D132" s="2" t="n">
-        <v>2889000</v>
+        <v>22652000</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Xiva Metall MChJ</t>
+          <t>Shodlik Poligraf AJ</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>297071667</t>
+          <t>307166732</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20208000210264664001</t>
+          <t>20208000026466438001</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Shartnoma №194/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата по счет-фактуре №6887 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>18.09.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5561,23 +5571,23 @@
           <t>223</t>
         </is>
       </c>
-      <c r="C133" s="2" t="n">
-        <v>11071000</v>
-      </c>
-      <c r="D133" s="2" t="n"/>
+      <c r="C133" s="2" t="n"/>
+      <c r="D133" s="2" t="n">
+        <v>9076000</v>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Mehnat Polimer XK</t>
+          <t>Denov Moy MChJ</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>203106510</t>
+          <t>335454567</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>20208000866576450001</t>
+          <t>20208000523414352001</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -5587,14 +5597,14 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №324</t>
+          <t>Оплата за това по с/ф №1559 от 04.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>18.09.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5602,23 +5612,23 @@
           <t>224</t>
         </is>
       </c>
-      <c r="C134" s="2" t="n">
-        <v>14352000</v>
-      </c>
-      <c r="D134" s="2" t="n"/>
+      <c r="C134" s="2" t="n"/>
+      <c r="D134" s="2" t="n">
+        <v>6169000</v>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Urganch Meva-Sabzavot MChJ</t>
+          <t>Navoiy Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>341863247</t>
+          <t>359568178</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>20208000901102914001</t>
+          <t>20208000926299217001</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -5628,14 +5638,14 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Transpor xizmatlari uchun to'lov, shartn. №193/26</t>
+          <t>Оплата за товар по счет-фактуре №5663 от 04.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5645,38 +5655,38 @@
       </c>
       <c r="C135" s="2" t="n"/>
       <c r="D135" s="2" t="n">
-        <v>5373000</v>
+        <v>21846000</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Shahrisabz Polimer AJ</t>
+          <t>Shodlik Poligraf AJ</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>307354545</t>
+          <t>307166732</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>20208000745234143001</t>
+          <t>20208000026466438001</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Shartnoma №203/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за товар по дог. №205/26 от 07.09.2026</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5686,38 +5696,38 @@
       </c>
       <c r="C136" s="2" t="n"/>
       <c r="D136" s="2" t="n">
-        <v>3116000</v>
+        <v>18900000</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Xiva Metall MChJ</t>
+          <t>Shodlik Poligraf AJ</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>297071667</t>
+          <t>307166732</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>20208000210264664001</t>
+          <t>20208000026466438001</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Shartnoma №267/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товар по счет-фактуре №4354 от 07.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5725,23 +5735,23 @@
           <t>227</t>
         </is>
       </c>
-      <c r="C137" s="2" t="n">
-        <v>43290000</v>
-      </c>
-      <c r="D137" s="2" t="n"/>
+      <c r="C137" s="2" t="n"/>
+      <c r="D137" s="2" t="n">
+        <v>12691000</v>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Nurafshon Non XK</t>
+          <t>Shodlik Poligraf AJ</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>243783821</t>
+          <t>307166732</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>20208000725266702001</t>
+          <t>20208000026466438001</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -5751,14 +5761,14 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №197/26</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №9080</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>22.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5768,38 +5778,38 @@
       </c>
       <c r="C138" s="2" t="n"/>
       <c r="D138" s="2" t="n">
-        <v>3621000</v>
+        <v>7248000</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Xiva Metall MChJ</t>
+          <t>Buxoro Mehmonxona AJ</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>297071667</t>
+          <t>270379692</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>20208000210264664001</t>
+          <t>20208000431871122001</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №4178 22.09.2026, QQS bilan</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №7431</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>22.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5809,38 +5819,38 @@
       </c>
       <c r="C139" s="2" t="n"/>
       <c r="D139" s="2" t="n">
-        <v>3093000</v>
+        <v>6438000</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Marg'ilon Trans Servis MChJ</t>
+          <t>Shodlik Poligraf AJ</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>384130722</t>
+          <t>307166732</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>20208000896978847001</t>
+          <t>20208000026466438001</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4681</t>
+          <t>Оплата за товар по счет-фактуре №5183 от 07.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>23.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5849,39 +5859,34 @@
         </is>
       </c>
       <c r="C140" s="2" t="n">
-        <v>8147000</v>
+        <v>37177000</v>
       </c>
       <c r="D140" s="2" t="n"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>201122905</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Уплата налога на добавленную стоимость за август</t>
+          <t>Ish haqi to'lovi avgust 2026 (plastik kartalarga)</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>24.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5889,40 +5894,40 @@
           <t>231</t>
         </is>
       </c>
-      <c r="C141" s="2" t="n"/>
-      <c r="D141" s="2" t="n">
-        <v>11729000</v>
-      </c>
+      <c r="C141" s="2" t="n">
+        <v>110917000</v>
+      </c>
+      <c r="D141" s="2" t="n"/>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Xiva Metall MChJ</t>
+          <t>Namangan Non XK</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>297071667</t>
+          <t>203301054</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>20208000210264664001</t>
+          <t>20208000769946250001</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №2712</t>
+          <t>Оплата за транспортные услуги по договору №188/26</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>24.09.2026</t>
+          <t>08.09.2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5931,22 +5936,22 @@
         </is>
       </c>
       <c r="C142" s="2" t="n">
-        <v>3087000</v>
+        <v>4940000</v>
       </c>
       <c r="D142" s="2" t="n"/>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Oqtosh Qurilish AJ</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>242569188</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>20208000464360672001</t>
+          <t>20208000399873134001</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -5956,14 +5961,14 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию согласно счету</t>
+          <t>Аренда помещения за сентябрь, дог. №5/24</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>09.09.2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5973,38 +5978,38 @@
       </c>
       <c r="C143" s="2" t="n"/>
       <c r="D143" s="2" t="n">
-        <v>230273000</v>
+        <v>10078000</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Shahrisabz Polimer AJ</t>
+          <t>Shodlik Poligraf AJ</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>307354545</t>
+          <t>307166732</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>20208000745234143001</t>
+          <t>20208000026466438001</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Shartnoma №171/26 bo'yicha oldindan to'lov</t>
+          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №8680 ОТ 09.09.2026, В Т.Ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>10.09.2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -6014,38 +6019,38 @@
       </c>
       <c r="C144" s="2" t="n"/>
       <c r="D144" s="2" t="n">
-        <v>19194000</v>
+        <v>19911000</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Xiva Metall MChJ</t>
+          <t>Denov Moy MChJ</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>297071667</t>
+          <t>335454567</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>20208000210264664001</t>
+          <t>20208000523414352001</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №233/26, QQS 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №4434</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>10.09.2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -6055,38 +6060,38 @@
       </c>
       <c r="C145" s="2" t="n"/>
       <c r="D145" s="2" t="n">
-        <v>8239000</v>
+        <v>8030000</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Ilhom Sut MChJ</t>
+          <t>Farovon Sut MChJ</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>204439781</t>
+          <t>269641343</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>20208000422619195001</t>
+          <t>20208000664060678001</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №6563 28.09.2026, QQS bilan</t>
+          <t>Оплата по счет-фактуре №5105 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>10.09.2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -6094,40 +6099,40 @@
           <t>236</t>
         </is>
       </c>
-      <c r="C146" s="2" t="n"/>
-      <c r="D146" s="2" t="n">
-        <v>3513000</v>
-      </c>
+      <c r="C146" s="2" t="n">
+        <v>11309000</v>
+      </c>
+      <c r="D146" s="2" t="n"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Xiva Metall MChJ</t>
+          <t>Namangan Non XK</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>297071667</t>
+          <t>203301054</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>20208000210264664001</t>
+          <t>20208000769946250001</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №204/26 от 28.09.2026</t>
+          <t>Оплата за товары согласно с/ф №7559</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>10.09.2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6136,39 +6141,34 @@
         </is>
       </c>
       <c r="C147" s="2" t="n">
-        <v>35382000</v>
+        <v>37100000</v>
       </c>
       <c r="D147" s="2" t="n"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Mehnat Polimer XK</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>203106510</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-1541)</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>20208000866576450001</t>
+          <t>16307000266463654417</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №108/26</t>
+          <t>Kredit shartnomasi L-2025-1541 bo'yicha navbatdagi to'lov (09.2026)</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>29.09.2026</t>
+          <t>11.09.2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -6176,23 +6176,23 @@
           <t>238</t>
         </is>
       </c>
-      <c r="C148" s="2" t="n"/>
-      <c r="D148" s="2" t="n">
-        <v>7544000</v>
-      </c>
+      <c r="C148" s="2" t="n">
+        <v>9233000</v>
+      </c>
+      <c r="D148" s="2" t="n"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Shahrisabz Polimer AJ</t>
+          <t>Nukus Logistik MChJ</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>307354545</t>
+          <t>210651038</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>20208000745234143001</t>
+          <t>20208000657645067001</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -6202,14 +6202,14 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №70/26 от 29.09.2026</t>
+          <t>Tovarlar uchun to'lov h/f №9492</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>29.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6219,38 +6219,38 @@
       </c>
       <c r="C149" s="2" t="n"/>
       <c r="D149" s="2" t="n">
-        <v>4480000</v>
+        <v>15160000</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Ilhom Sut MChJ</t>
+          <t>Shahrisabz Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>204439781</t>
+          <t>301266775</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>20208000422619195001</t>
+          <t>20208000866099754001</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №3943</t>
+          <t>Оплата за продукцию по договору №192/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>30.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -6259,34 +6259,39 @@
         </is>
       </c>
       <c r="C150" s="2" t="n">
-        <v>300000</v>
+        <v>30296000</v>
       </c>
       <c r="D150" s="2" t="n"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Lazzat Mehmonxona MChJ</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>286324779</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000110291460001</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Hisob-kassa xizmati uchun haq</t>
+          <t>Оплата за товары согласно счет-фактуре №4876</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>30.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -6294,23 +6299,23 @@
           <t>241</t>
         </is>
       </c>
-      <c r="C151" s="2" t="n">
-        <v>37427000</v>
-      </c>
-      <c r="D151" s="2" t="n"/>
+      <c r="C151" s="2" t="n"/>
+      <c r="D151" s="2" t="n">
+        <v>9404000</v>
+      </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Mehnat Polimer XK</t>
+          <t>Denov Moy MChJ</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>203106510</t>
+          <t>335454567</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>20208000866576450001</t>
+          <t>20208000523414352001</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -6320,14 +6325,14 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №252/26</t>
+          <t>Оплата за продукцию по договору №131/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>30.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -6336,58 +6341,1078 @@
         </is>
       </c>
       <c r="C152" s="2" t="n">
-        <v>161159000</v>
+        <v>5070000</v>
       </c>
       <c r="D152" s="2" t="n"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Nurafshon Non XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>243783821</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>20208000725266702001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №142/26</t>
+          <t>Avgust oyi uchun ijtimoiy soliq</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Jami aylanma:</t>
-        </is>
-      </c>
-      <c r="C153" s="4" t="n">
-        <v>1903853000</v>
-      </c>
-      <c r="D153" s="4" t="n">
-        <v>1935253000</v>
+          <t>15.09.2026</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="n">
+        <v>5070000</v>
+      </c>
+      <c r="D153" s="2" t="n"/>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>201122905</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>23402000300100001010</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>00014</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Налог на доходы физических лиц за август 2026 г.</t>
+        </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
+          <t>17.09.2026</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="n"/>
+      <c r="D154" s="2" t="n">
+        <v>50300000</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Shodlik Poligraf AJ</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>307166732</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>20208000026466438001</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Оплата за продукцию по договору №283/26, НДС 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>17.09.2026</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="n"/>
+      <c r="D155" s="2" t="n">
+        <v>26104000</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Bunyodkor Mato MChJ</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>243978194</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>20208000261919541001</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Оплата по счет-фактуре №8017 за поставленный товар</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>17.09.2026</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="n">
+        <v>12050000</v>
+      </c>
+      <c r="D156" s="2" t="n"/>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Angren Metall Servis MChJ</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>328433928</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>20208000706941050001</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Оплата за товары согласно счет-фактуре №5584</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>21.09.2026</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="n"/>
+      <c r="D157" s="2" t="n">
+        <v>108332000</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Shodlik Poligraf AJ</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>307166732</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>20208000026466438001</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Оплата за товар по счет-фактуре №1110 от 21.09.2026, в т.ч. НДС 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>21.09.2026</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="n"/>
+      <c r="D158" s="2" t="n">
+        <v>81382000</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Denov Moy MChJ</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>335454567</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>20208000523414352001</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Оплата за товар по счет-фактуре №6050 от 21.09.2026, в т.ч. НДС 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>21.09.2026</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="n"/>
+      <c r="D159" s="2" t="n">
+        <v>16334000</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Shodlik Poligraf AJ</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>307166732</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>20208000026466438001</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Оплата запродукцию по договору №102/26, НДС 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>21.09.2026</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="n"/>
+      <c r="D160" s="2" t="n">
+        <v>12200000</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Shodlik Poligraf AJ</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>307166732</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>20208000026466438001</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №7/26, НДС 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>21.09.2026</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="n"/>
+      <c r="D161" s="2" t="n">
+        <v>9390000</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Shahrisabz Avto Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>301266775</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>20208000866099754001</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Оплата по с/ф №2883 за поставленный товар</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>21.09.2026</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="n">
+        <v>8179000</v>
+      </c>
+      <c r="D162" s="2" t="n"/>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>201122905</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>23402000300100001010</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>00014</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>НДС за август 2026 г.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>21.09.2026</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="n">
+        <v>29129000</v>
+      </c>
+      <c r="D163" s="2" t="n"/>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Xiva Yog'och AJ</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>225139006</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>20208000839218846001</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Transport xizmtlari uchun to'lov, shartnoma №288/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>21.09.2026</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="n">
+        <v>104264000</v>
+      </c>
+      <c r="D164" s="2" t="n"/>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Nukus Logistik MChJ</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>210651038</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>20208000657645067001</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Оплата за транспортные услуги по договору №71/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>22.09.2026</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="n"/>
+      <c r="D165" s="2" t="n">
+        <v>105649000</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Navoiy Avto Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>359568178</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>20208000926299217001</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Оплата за товар по с/ф №3778 от 22.09.2026, в т.ч. НДС 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>22.09.2026</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="n"/>
+      <c r="D166" s="2" t="n">
+        <v>21860000</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Shodlik Poligraf AJ</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>307166732</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>20208000026466438001</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №267/26, QQS 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>22.09.2026</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="n"/>
+      <c r="D167" s="2" t="n">
+        <v>17867000</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Shodlik Poligraf AJ</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>307166732</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>20208000026466438001</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Оплата по с/ф №6828 за поставленный товар</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>23.09.2026</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="n">
+        <v>3087000</v>
+      </c>
+      <c r="D168" s="2" t="n"/>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Hududiy elektr tarmoqlari AJ</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>200933985</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>20208000962245549001</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Оплата за электроэнергию за сентябрь 2026 г.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>23.09.2026</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="n">
+        <v>25213000</v>
+      </c>
+      <c r="D169" s="2" t="n"/>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Lazzat Mehmonxona MChJ</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>286324779</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>20208000110291460001</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Оплата за товары согласно с/ф №7453</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>25.09.2026</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="n"/>
+      <c r="D170" s="2" t="n">
+        <v>9558000</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Shahrisabz Avto Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>301266775</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>20208000866099754001</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Оплата за товар по счет-фактуре №9395 от 25.09.2026, в т.ч. НДС 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>25.09.2026</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="n">
+        <v>66009000</v>
+      </c>
+      <c r="D171" s="2" t="n"/>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Namangan Non XK</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>203301054</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>20208000769946250001</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Tovarlar uchun to'lov h/f №8046</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="n"/>
+      <c r="D172" s="2" t="n">
+        <v>13464000</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Shodlik Poligraf AJ</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>307166732</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>20208000026466438001</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Оплата по с/ф №5972 за поставленный товар</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="n">
+        <v>78659000</v>
+      </c>
+      <c r="D173" s="2" t="n"/>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Nukus Logistik MChJ</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>210651038</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>20208000657645067001</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Оплата за сырье по договору №93/26 от 28.09.2026, НДС 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="n"/>
+      <c r="D174" s="2" t="n">
+        <v>7686000</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Bunyodkor Mato MChJ</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>243978194</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>20208000261919541001</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Предоплата за товар по договору №40/26 от 29.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="n">
+        <v>48459000</v>
+      </c>
+      <c r="D175" s="2" t="n"/>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Namangan Non XK</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>203301054</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>20208000769946250001</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Оплата за упаковочные материалы, с/ф №7071</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>30.09.2026</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D176" s="2" t="n"/>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Yangi Asr Bank</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>45994000900000001001</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Комиссия за перевод</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>30.09.2026</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="n">
+        <v>18427000</v>
+      </c>
+      <c r="D177" s="2" t="n"/>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Namangan Non XK</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>203301054</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>20208000769946250001</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Xom ashyo uchun to'lov, shartnoma №44/26, QQS bilan</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Jami aylanma:</t>
+        </is>
+      </c>
+      <c r="C178" s="4" t="n">
+        <v>1889350000</v>
+      </c>
+      <c r="D178" s="4" t="n">
+        <v>1920750000</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
           <t>Davr oxiridagi qoldiq:</t>
         </is>
       </c>
-      <c r="C154" s="4" t="n">
+      <c r="C179" s="4" t="n">
         <v>216900000</v>
       </c>
-      <c r="D154" s="4" t="n"/>
+      <c r="D179" s="4" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
